--- a/Result/profitability/5471.xlsx
+++ b/Result/profitability/5471.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.85</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3</v>
+        <v>0.3725</v>
       </c>
       <c r="N2" t="n">
-        <v>41.2725</v>
+        <v>41.3075</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.57</v>
       </c>
       <c r="M3" t="n">
-        <v>0.47875</v>
+        <v>0.5425</v>
       </c>
       <c r="N3" t="n">
-        <v>41.285</v>
+        <v>41.25</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.56</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6475</v>
+        <v>0.70875</v>
       </c>
       <c r="N4" t="n">
-        <v>41.1425</v>
+        <v>41.0675</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>0.68875</v>
+        <v>0.775</v>
       </c>
       <c r="N5" t="n">
-        <v>40.21875</v>
+        <v>39.94625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.6</v>
       </c>
       <c r="M6" t="n">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="N6" t="n">
-        <v>39.8725</v>
+        <v>40.02875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.17</v>
       </c>
       <c r="M7" t="n">
-        <v>0.87625</v>
+        <v>0.93875</v>
       </c>
       <c r="N7" t="n">
-        <v>40.14125</v>
+        <v>40.12</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.52</v>
       </c>
       <c r="M8" t="n">
-        <v>1.03875</v>
+        <v>1.06875</v>
       </c>
       <c r="N8" t="n">
-        <v>40.3575</v>
+        <v>40.15</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1648,7 +1648,7 @@
         <v>1.20125</v>
       </c>
       <c r="N10" t="n">
-        <v>40.43</v>
+        <v>40.42999999999999</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1902,7 +1902,7 @@
         <v>1.15125</v>
       </c>
       <c r="N12" t="n">
-        <v>41.5925</v>
+        <v>41.59249999999999</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5471</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>945</v>
+      </c>
+      <c r="D75" t="n">
+        <v>559</v>
+      </c>
+      <c r="E75" t="n">
+        <v>387</v>
+      </c>
+      <c r="F75" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="G75" t="n">
+        <v>105</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>11.12%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>30</v>
+      </c>
+      <c r="J75" t="n">
+        <v>135</v>
+      </c>
+      <c r="K75" t="n">
+        <v>121</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.28375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>41.32</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.660000000000004</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.03900375939849632</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-2.18</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.05060352831940573</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
